--- a/docs/Learning_Implementation_Summary.xlsx
+++ b/docs/Learning_Implementation_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Learning\LearningApp\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3393A07D-A8CC-4E83-A2D1-CC035A043F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B251E8AD-ADE0-47FB-8F7B-D734B0DBF283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="2" xr2:uid="{67DF34DB-73ED-4182-9C7A-802B974A01BC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{67DF34DB-73ED-4182-9C7A-802B974A01BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -773,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -798,6 +798,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1272,10 +1275,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
         <v>144</v>
       </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
@@ -1808,6 +1813,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:C3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>